--- a/education_forms/047_student_academic_records_release_form--education_forms.xlsx
+++ b/education_forms/047_student_academic_records_release_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,8 +619,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -682,12 +682,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Family Member'}</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'school'}</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'School'}</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'transcript'}</t>
+          <t>transcript</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Transcript'}</t>
+          <t>Transcript</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'letter_of_good_standing'}</t>
+          <t>letter_of_good_standing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Letter of Good Standing'}</t>
+          <t>Letter of Good Standing</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other_academic_records'}</t>
+          <t>other_academic_records</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other Academic Records'}</t>
+          <t>Other Academic Records</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
